--- a/data/trans_camb/IP1012-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1012-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,37</t>
+          <t>0,0; 9,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,91</t>
+          <t>0,0; 8,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,98</t>
+          <t>0,54; 5,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,24; -0,59</t>
+          <t>-6,21; -0,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,24; -0,59</t>
+          <t>-6,21; -0,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; -0,3</t>
+          <t>-3,0; -0,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; -0,31</t>
+          <t>-3,0; -0,3</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,28</t>
+          <t>0,0; 4,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 1,61</t>
+          <t>-2,59; 1,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 0,0</t>
+          <t>-4,27; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,95</t>
+          <t>-0,92; 1,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,0</t>
+          <t>-2,24; 0,0</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 6,75</t>
+          <t>-3,13; 5,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 0,0</t>
+          <t>-7,65; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1270,17 +1270,17 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,85</t>
+          <t>0,0; 6,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,82</t>
+          <t>-1,49; 3,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 1,39</t>
+          <t>-2,24; 2,03</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,08</t>
+          <t>0,0; 6,48</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,89</t>
+          <t>0,0; 5,85</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,43</t>
+          <t>0,0; 4,89</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,0</t>
+          <t>-2,84; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 0,0</t>
+          <t>-3,19; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 3,14</t>
+          <t>-1,97; 3,29</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 2,46</t>
+          <t>-1,92; 2,54</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,41</t>
+          <t>-1,46; 1,5</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,96</t>
+          <t>-1,57; 0,99</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,0</t>
+          <t>-2,37; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 0,0</t>
+          <t>-1,97; 0,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,77</t>
+          <t>-1,71; 0,77</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 0,0</t>
+          <t>-2,55; 0,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,39</t>
+          <t>-1,26; 0,39</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,0</t>
+          <t>-1,47; 0,0</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,85</t>
+          <t>-0,38; 0,8</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,81; -0,09</t>
+          <t>-0,8; -0,09</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,85</t>
+          <t>-0,76; 0,86</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,17</t>
+          <t>-1,17; 0,12</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,6</t>
+          <t>-0,35; 0,61</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,74; -0,0</t>
+          <t>-0,82; -0,06</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1965,22 +1965,22 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-70,0; 197,79</t>
+          <t>-66,91; 233,53</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-90,71; 59,63</t>
+          <t>-90,24; 66,22</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-51,11; 186,79</t>
+          <t>-48,92; 185,47</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-91,69; 26,51</t>
+          <t>-92,2; 12,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1012-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1012-Provincia-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,31</t>
+          <t>0,0; 8,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,17</t>
+          <t>0,0; 7,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,54</t>
+          <t>0,53; 5,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,21; -0,59</t>
+          <t>-5,71; -0,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,21; -0,59</t>
+          <t>-5,71; -0,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,0; -0,3</t>
+          <t>-3,49; -0,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,0; -0,3</t>
+          <t>-3,44; -0,31</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,34</t>
+          <t>0,0; 4,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,59</t>
+          <t>-3,4; 1,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 0,0</t>
+          <t>-4,23; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,64</t>
+          <t>-0,91; 1,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,0</t>
+          <t>-2,18; 0,0</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 5,25</t>
+          <t>-3,08; 5,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1270,17 +1270,17 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,81</t>
+          <t>0,0; 6,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 3,32</t>
+          <t>-1,49; 2,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 2,03</t>
+          <t>-2,25; 2,05</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,48</t>
+          <t>0,0; 8,03</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,85</t>
+          <t>0,0; 5,83</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,89</t>
+          <t>0,0; 5,44</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 0,0</t>
+          <t>-3,24; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,0</t>
+          <t>-3,17; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 3,29</t>
+          <t>-1,93; 3,52</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,54</t>
+          <t>-2,4; 2,06</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,5</t>
+          <t>-1,27; 1,52</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,99</t>
+          <t>-1,54; 1,05</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 539,48</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,0</t>
+          <t>-2,01; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,0</t>
+          <t>-2,0; 0,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 0,77</t>
+          <t>-1,6; 0,78</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 0,0</t>
+          <t>-2,14; 0,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,39</t>
+          <t>-1,08; 0,36</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,0</t>
+          <t>-1,41; 0,0</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,8</t>
+          <t>-0,35; 0,73</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,8; -0,09</t>
+          <t>-0,83; -0,09</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,86</t>
+          <t>-0,81; 0,76</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,12</t>
+          <t>-1,14; 0,16</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,61</t>
+          <t>-0,39; 0,58</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,82; -0,06</t>
+          <t>-0,79; -0,05</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 793,42</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1965,22 +1965,22 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-66,91; 233,53</t>
+          <t>-71,01; 183,28</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-90,24; 66,22</t>
+          <t>-89,86; 62,97</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-48,92; 185,47</t>
+          <t>-56,36; 167,91</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-92,2; 12,04</t>
+          <t>-91,87; 20,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1012-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1012-Provincia-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,17 +593,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>1,75</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,32</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,62</t>
+          <t>0,0; 7,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,44</t>
+          <t>0,0; 10,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,86</t>
+          <t>0,54; 5,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,18</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,18</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,18</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,18</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,24; -0,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,24; -0,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,71; -0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,71; -0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,49; -0,31</t>
+          <t>-3,04; -0,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; -0,31</t>
+          <t>-3,23; -0,31</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -948,17 +948,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,08</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,85</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,84</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,27 +1099,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,31</t>
+          <t>-2,57; 1,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,61; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 1,56</t>
+          <t>0,0; 4,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,65</t>
+          <t>-0,9; 1,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-9,45%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-9,45%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1,33</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,17</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-1,53</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 0,0</t>
+          <t>0,0; 5,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,1; 6,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,65</t>
+          <t>-7,5; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,81</t>
+          <t>-1,5; 2,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 2,05</t>
+          <t>-2,28; 1,39</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>10,85%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1373,17 +1373,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>1,64</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,03</t>
+          <t>0,0; 5,89</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,83</t>
+          <t>0,0; 9,08</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,44</t>
+          <t>0,0; 4,43</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,04</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>-0,57</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-0,57</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,04</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 0,0</t>
+          <t>-1,95; 3,14</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,0</t>
+          <t>-2,3; 2,46</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 3,52</t>
+          <t>-2,85; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,06</t>
+          <t>-3,41; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 1,52</t>
+          <t>-1,46; 1,41</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,05</t>
+          <t>-1,55; 0,96</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>28,11%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>28,11%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 539,48</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-0,05</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-0,43</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>-0,4</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>-0,4</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,0</t>
+          <t>-1,61; 0,77</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,0</t>
+          <t>-2,15; 0,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,78</t>
+          <t>-1,88; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,0</t>
+          <t>-2,02; 0,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,36</t>
+          <t>-1,08; 0,39</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,0</t>
+          <t>-1,27; 0,0</t>
         </is>
       </c>
     </row>
@@ -1761,17 +1761,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-10,79%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-10,79%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>0,02</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,42</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>0,16</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>-0,29</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-0,42</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,73</t>
+          <t>-0,75; 0,85</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,83; -0,09</t>
+          <t>-1,15; 0,17</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,76</t>
+          <t>-0,27; 0,85</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,16</t>
+          <t>-0,81; -0,09</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,58</t>
+          <t>-0,37; 0,6</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,79; -0,05</t>
+          <t>-0,74; -0,0</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-53,34%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>55,52%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-53,34%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 793,42</t>
+          <t>-70,0; 197,79</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,71; 59,63</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-71,01; 183,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-89,86; 62,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-56,36; 167,91</t>
+          <t>-51,11; 186,79</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-91,87; 20,78</t>
+          <t>-91,69; 26,51</t>
         </is>
       </c>
     </row>
